--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_reports/desktop_ui_summary.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_reports/desktop_ui_summary.xlsx
@@ -488,34 +488,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1489653337645632</v>
+        <v>0.1512893293587264</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Agreeableness, Conscientiousness, Neuroticism</t>
+          <t>Conscientiousness, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.1490, 0.1471, 0.1392</t>
+          <t>0.1513, 0.1451, 0.1404</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Openness, Agreeableness, current_mood</t>
+          <t>Neuroticism, Conscientiousness, primary_persona</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0256, 0.0248, 0.0223</t>
+          <t>0.0281, 0.0276, 0.0244</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.02560316819262314</v>
+        <v>0.02811945678219669</v>
       </c>
     </row>
     <row r="3">
@@ -535,30 +535,30 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1516035561058999</v>
+        <v>0.1586560731382151</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, primary_persona</t>
+          <t>Neuroticism, Openness, primary_persona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.1516, 0.1495, 0.1406</t>
+          <t>0.1587, 0.1431, 0.1402</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_device, current_mood</t>
+          <t>primary_device, Neuroticism, current_mood</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0366, 0.0360, 0.0338</t>
+          <t>0.0334, 0.0326, 0.0306</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.03661318172966233</v>
+        <v>0.03341680169935241</v>
       </c>
     </row>
     <row r="4">
@@ -574,34 +574,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1475917128710594</v>
+        <v>0.1498991259733833</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, primary_persona</t>
+          <t>Conscientiousness, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.1476, 0.1420, 0.1413</t>
+          <t>0.1499, 0.1487, 0.1460</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Agreeableness</t>
+          <t>Conscientiousness, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0350, 0.0318, 0.0282</t>
+          <t>0.0396, 0.0389, 0.0335</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.03501225697927684</v>
+        <v>0.03963501720258204</v>
       </c>
     </row>
     <row r="5">
@@ -621,30 +621,30 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1734640320746739</v>
+        <v>0.1594405556880039</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Conscientiousness</t>
+          <t>Neuroticism, Openness, Agreeableness</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.1735, 0.1500, 0.1410</t>
+          <t>0.1594, 0.1509, 0.1396</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>primary_device, Openness, Agreeableness</t>
+          <t>Conscientiousness, primary_device, Extraversion</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0450, 0.0338, 0.0299</t>
+          <t>0.0376, 0.0308, 0.0273</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.04497102499333076</v>
+        <v>0.03764689293797543</v>
       </c>
     </row>
     <row r="6">
@@ -664,30 +664,30 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1469126294681928</v>
+        <v>0.1538892887108169</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, primary_persona</t>
+          <t>Neuroticism, Openness, Agreeableness</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.1469, 0.1438, 0.1381</t>
+          <t>0.1539, 0.1477, 0.1402</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agreeableness, primary_device, Neuroticism</t>
+          <t>current_mood, Neuroticism, primary_device</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0352, 0.0336, 0.0330</t>
+          <t>0.0358, 0.0293, 0.0250</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.03521455900801927</v>
+        <v>0.03582976720680696</v>
       </c>
     </row>
     <row r="7">
@@ -707,30 +707,30 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1688294095120784</v>
+        <v>0.1554617319292695</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, Conscientiousness</t>
+          <t>Neuroticism, Agreeableness, Extraversion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.1688, 0.1579, 0.1316</t>
+          <t>0.1555, 0.1495, 0.1433</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Extraversion, primary_persona, Agreeableness</t>
+          <t>current_mood, Agreeableness, Conscientiousness</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0495, 0.0354, 0.0254</t>
+          <t>0.0367, 0.0297, 0.0262</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.04953568965636855</v>
+        <v>0.03669277804637983</v>
       </c>
     </row>
     <row r="8">
@@ -750,30 +750,30 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1593344978022734</v>
+        <v>0.1621265897738878</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Extraversion</t>
+          <t>Neuroticism, Conscientiousness, Agreeableness</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.1593, 0.1521, 0.1386</t>
+          <t>0.1621, 0.1396, 0.1376</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agreeableness, primary_persona, current_mood</t>
+          <t>primary_persona, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0364, 0.0330, 0.0246</t>
+          <t>0.0311, 0.0309, 0.0302</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.0363836631085862</v>
+        <v>0.03110389560142154</v>
       </c>
     </row>
     <row r="9">
@@ -793,30 +793,30 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1601909869000728</v>
+        <v>0.156096636722261</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.1602, 0.1421, 0.1375</t>
+          <t>0.1561, 0.1416, 0.1347</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Agreeableness</t>
+          <t>Neuroticism, primary_persona, Agreeableness</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0282, 0.0246, 0.0242</t>
+          <t>0.0289, 0.0260, 0.0259</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.02815128451829332</v>
+        <v>0.02885014099936915</v>
       </c>
     </row>
     <row r="10">
@@ -836,30 +836,30 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1487447892060389</v>
+        <v>0.150012559438695</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Agreeableness</t>
+          <t>Neuroticism, primary_persona, Extraversion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.1487, 0.1481, 0.1383</t>
+          <t>0.1500, 0.1493, 0.1394</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Conscientiousness, Openness, primary_device</t>
+          <t>primary_persona, Neuroticism, Conscientiousness</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0401, 0.0351, 0.0288</t>
+          <t>0.0362, 0.0331, 0.0260</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.04011943385433388</v>
+        <v>0.03622596838859769</v>
       </c>
     </row>
     <row r="11">
@@ -879,30 +879,30 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1557646206679608</v>
+        <v>0.1515395151341888</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, primary_persona</t>
+          <t>Agreeableness, current_mood, Extraversion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.1558, 0.1554, 0.1418</t>
+          <t>0.1515, 0.1473, 0.1390</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Extraversion, current_mood, Openness</t>
+          <t>Neuroticism, primary_persona, current_mood</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0467, 0.0425, 0.0277</t>
+          <t>0.0498, 0.0293, 0.0269</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.04672734454016356</v>
+        <v>0.04976062206013869</v>
       </c>
     </row>
     <row r="12">
@@ -922,30 +922,30 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1670212648937824</v>
+        <v>0.162995294493098</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neuroticism, current_mood, Openness</t>
+          <t>Neuroticism, current_mood, Extraversion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.1670, 0.1461, 0.1320</t>
+          <t>0.1630, 0.1601, 0.1382</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Openness, primary_persona, Extraversion</t>
+          <t>Agreeableness, current_mood, Extraversion</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0360, 0.0356, 0.0297</t>
+          <t>0.0421, 0.0400, 0.0383</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.03601509161981057</v>
+        <v>0.04210615145277036</v>
       </c>
     </row>
     <row r="13">
@@ -961,34 +961,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Agreeableness</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.160271276894365</v>
+        <v>0.1578908535418077</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Agreeableness, Neuroticism, Openness</t>
+          <t>Neuroticism, Agreeableness, Openness</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.1603, 0.1588, 0.1342</t>
+          <t>0.1579, 0.1534, 0.1426</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Extraversion, current_mood, primary_device</t>
+          <t>primary_persona, Extraversion, primary_device</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0285, 0.0277, 0.0235</t>
+          <t>0.0349, 0.0310, 0.0262</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.02853896711768724</v>
+        <v>0.03492245695292501</v>
       </c>
     </row>
     <row r="14">
@@ -1004,34 +1004,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neuroticism</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1573615280668692</v>
+        <v>0.1590698535013453</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Agreeableness</t>
+          <t>Conscientiousness, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.1574, 0.1515, 0.1353</t>
+          <t>0.1591, 0.1504, 0.1461</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neuroticism, current_mood, Extraversion</t>
+          <t>current_mood, primary_device, Extraversion</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0367, 0.0305, 0.0299</t>
+          <t>0.0360, 0.0351, 0.0340</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.03666279100423075</v>
+        <v>0.03597010550148029</v>
       </c>
     </row>
   </sheetData>
